--- a/source_data/Extended_Data_Fig_1_source_data.xlsx
+++ b/source_data/Extended_Data_Fig_1_source_data.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>a, Mean GCIRI of cities in the lowest and highest quartiles of local hazard within each income group. b, Median GCIRI and interquartile range across within-group deciles of the local hazard ratio H, the mean ratio of a city's hazard intensities to the national means of the same hazards (Methods). c, Weakest capacity by city population class, with 3,981, 1,363, 431, 52 and 35 cities from the smallest to the largest class. Strengths are direction-corrected so that higher values are better.</t>
+          <t>a, Mean GCIRI of cities in the weakest (open circles) and strongest (filled circles) quartiles of local hazard within each income group. b, Median GCIRI and interquartile range across within-group deciles of the local hazard ratio H, the mean ratio of a city's hazard intensities to the national means of the same hazards (Methods). c, Mean GCIRI by city population class and income group. Open symbols mark classes with fewer than ten cities, with the number of cities shown. d, Weakest capacity by city population class, with 3,981, 1,363, 431, 52 and 35 cities from the smallest to the largest class. Strengths are direction-corrected so that higher values are better.</t>
         </is>
       </c>
     </row>
@@ -590,13 +590,13 @@
         <v>821</v>
       </c>
       <c r="C2" t="n">
-        <v>87.04504854368932</v>
+        <v>87.16582524271843</v>
       </c>
       <c r="D2" t="n">
-        <v>80.03658536585365</v>
+        <v>80.03043902439023</v>
       </c>
       <c r="E2" t="n">
-        <v>7.008463177835665</v>
+        <v>7.135386218328193</v>
       </c>
     </row>
     <row r="3">
@@ -609,13 +609,13 @@
         <v>1979</v>
       </c>
       <c r="C3" t="n">
-        <v>72.16650505050505</v>
+        <v>72.17535353535354</v>
       </c>
       <c r="D3" t="n">
-        <v>56.6570101010101</v>
+        <v>56.66555555555556</v>
       </c>
       <c r="E3" t="n">
-        <v>15.50949494949495</v>
+        <v>15.50979797979798</v>
       </c>
     </row>
     <row r="4">
@@ -647,13 +647,13 @@
         <v>495</v>
       </c>
       <c r="C5" t="n">
-        <v>39.08451612903225</v>
+        <v>39.08217741935484</v>
       </c>
       <c r="D5" t="n">
         <v>11.49024193548387</v>
       </c>
       <c r="E5" t="n">
-        <v>27.59427419354838</v>
+        <v>27.59193548387097</v>
       </c>
     </row>
   </sheetData>
@@ -720,13 +720,13 @@
         <v>0.6999</v>
       </c>
       <c r="D2" t="n">
-        <v>87.76000000000001</v>
+        <v>87.87</v>
       </c>
       <c r="E2" t="n">
         <v>84.43000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>92.64</v>
+        <v>92.995</v>
       </c>
       <c r="G2" t="n">
         <v>83</v>
@@ -745,13 +745,13 @@
         <v>0.7479</v>
       </c>
       <c r="D3" t="n">
-        <v>88.90000000000001</v>
+        <v>88.74000000000001</v>
       </c>
       <c r="E3" t="n">
         <v>83.6525</v>
       </c>
       <c r="F3" t="n">
-        <v>92.84999999999999</v>
+        <v>93.07250000000001</v>
       </c>
       <c r="G3" t="n">
         <v>82</v>
@@ -770,13 +770,13 @@
         <v>0.78235</v>
       </c>
       <c r="D4" t="n">
-        <v>88.16</v>
+        <v>88.16999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>81.60249999999999</v>
+        <v>81.535</v>
       </c>
       <c r="F4" t="n">
-        <v>91.795</v>
+        <v>91.77249999999999</v>
       </c>
       <c r="G4" t="n">
         <v>82</v>
@@ -795,13 +795,13 @@
         <v>0.8228</v>
       </c>
       <c r="D5" t="n">
-        <v>88.44</v>
+        <v>88.405</v>
       </c>
       <c r="E5" t="n">
-        <v>82.5275</v>
+        <v>82.83750000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>92.3275</v>
+        <v>92.4025</v>
       </c>
       <c r="G5" t="n">
         <v>82</v>
@@ -820,13 +820,13 @@
         <v>0.8647499999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>85.215</v>
+        <v>85.30500000000001</v>
       </c>
       <c r="E6" t="n">
         <v>79.9875</v>
       </c>
       <c r="F6" t="n">
-        <v>89.50750000000001</v>
+        <v>89.505</v>
       </c>
       <c r="G6" t="n">
         <v>82</v>
@@ -845,13 +845,13 @@
         <v>0.91095</v>
       </c>
       <c r="D7" t="n">
-        <v>85.13999999999999</v>
+        <v>85.375</v>
       </c>
       <c r="E7" t="n">
         <v>78.7</v>
       </c>
       <c r="F7" t="n">
-        <v>90.39</v>
+        <v>90.38249999999999</v>
       </c>
       <c r="G7" t="n">
         <v>82</v>
@@ -870,13 +870,13 @@
         <v>0.97205</v>
       </c>
       <c r="D8" t="n">
-        <v>85.2</v>
+        <v>85.265</v>
       </c>
       <c r="E8" t="n">
-        <v>75.16250000000001</v>
+        <v>75.2375</v>
       </c>
       <c r="F8" t="n">
-        <v>92.75749999999999</v>
+        <v>93.01000000000001</v>
       </c>
       <c r="G8" t="n">
         <v>82</v>
@@ -895,13 +895,13 @@
         <v>1.0577</v>
       </c>
       <c r="D9" t="n">
-        <v>82.96000000000001</v>
+        <v>83.27500000000001</v>
       </c>
       <c r="E9" t="n">
         <v>73.82000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>89.77499999999999</v>
+        <v>90.0975</v>
       </c>
       <c r="G9" t="n">
         <v>82</v>
@@ -920,13 +920,13 @@
         <v>1.20375</v>
       </c>
       <c r="D10" t="n">
-        <v>87.09</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>80.395</v>
+        <v>80.91249999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>90.9375</v>
+        <v>90.9675</v>
       </c>
       <c r="G10" t="n">
         <v>82</v>
@@ -945,10 +945,10 @@
         <v>1.7714</v>
       </c>
       <c r="D11" t="n">
-        <v>77.02500000000001</v>
+        <v>77.89</v>
       </c>
       <c r="E11" t="n">
-        <v>71.3725</v>
+        <v>70.485</v>
       </c>
       <c r="F11" t="n">
         <v>86.94499999999999</v>
@@ -976,7 +976,7 @@
         <v>70.44750000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>78.91</v>
+        <v>79.185</v>
       </c>
       <c r="G12" t="n">
         <v>198</v>
@@ -1755,13 +1755,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12.58477769404672</v>
+        <v>12.55965837729214</v>
       </c>
       <c r="C2" t="n">
         <v>21.10022607385079</v>
       </c>
       <c r="D2" t="n">
-        <v>66.31499623210249</v>
+        <v>66.34011554885707</v>
       </c>
       <c r="E2" t="n">
         <v>3981</v>
@@ -1774,13 +1774,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24.57813646368305</v>
+        <v>24.65150403521644</v>
       </c>
       <c r="C3" t="n">
         <v>24.57813646368305</v>
       </c>
       <c r="D3" t="n">
-        <v>50.8437270726339</v>
+        <v>50.77035950110052</v>
       </c>
       <c r="E3" t="n">
         <v>1363</v>
@@ -1894,7 +1894,7 @@
         <v>539</v>
       </c>
       <c r="D2" t="n">
-        <v>83.51339517625232</v>
+        <v>83.58113172541745</v>
       </c>
     </row>
     <row r="3">
@@ -1912,7 +1912,7 @@
         <v>184</v>
       </c>
       <c r="D3" t="n">
-        <v>84.28038043478261</v>
+        <v>84.18983695652175</v>
       </c>
     </row>
     <row r="4">
@@ -1930,7 +1930,7 @@
         <v>83</v>
       </c>
       <c r="D4" t="n">
-        <v>85.88036144578312</v>
+        <v>85.89746987951807</v>
       </c>
     </row>
     <row r="5">
@@ -1948,7 +1948,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>84.73888888888888</v>
+        <v>84.42222222222222</v>
       </c>
     </row>
     <row r="6">
@@ -1966,7 +1966,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>86.67666666666666</v>
+        <v>86.795</v>
       </c>
     </row>
     <row r="7">
@@ -1984,7 +1984,7 @@
         <v>1294</v>
       </c>
       <c r="D7" t="n">
-        <v>64.97994590417311</v>
+        <v>64.98615919629057</v>
       </c>
     </row>
     <row r="8">
@@ -2002,7 +2002,7 @@
         <v>511</v>
       </c>
       <c r="D8" t="n">
-        <v>65.56101761252447</v>
+        <v>65.56737769080235</v>
       </c>
     </row>
     <row r="9">
@@ -2020,7 +2020,7 @@
         <v>145</v>
       </c>
       <c r="D9" t="n">
-        <v>66.36606896551724</v>
+        <v>66.38620689655173</v>
       </c>
     </row>
     <row r="10">
@@ -2038,7 +2038,7 @@
         <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>67.91333333333334</v>
+        <v>67.96933333333332</v>
       </c>
     </row>
     <row r="11">
@@ -2056,7 +2056,7 @@
         <v>14</v>
       </c>
       <c r="D11" t="n">
-        <v>70.42928571428571</v>
+        <v>70.46714285714286</v>
       </c>
     </row>
     <row r="12">
@@ -2074,7 +2074,7 @@
         <v>1749</v>
       </c>
       <c r="D12" t="n">
-        <v>37.74899371069183</v>
+        <v>37.74881074899943</v>
       </c>
     </row>
     <row r="13">
@@ -2164,7 +2164,7 @@
         <v>369</v>
       </c>
       <c r="D17" t="n">
-        <v>29.91376693766938</v>
+        <v>29.9129810298103</v>
       </c>
     </row>
     <row r="18">
@@ -2182,7 +2182,7 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>23.21766666666667</v>
+        <v>23.21711111111111</v>
       </c>
     </row>
     <row r="19">
